--- a/Backtest/01-10-20/S&P500stock_01-10-20period252RS90.xlsx
+++ b/Backtest/01-10-20/S&P500stock_01-10-20period252RS90.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="80">
   <si>
     <t>Stock</t>
   </si>
@@ -127,112 +127,133 @@
     <t>EM Rating</t>
   </si>
   <si>
-    <t>CRM</t>
-  </si>
-  <si>
-    <t>FDX</t>
-  </si>
-  <si>
-    <t>CHTR</t>
-  </si>
-  <si>
-    <t>CRWD</t>
-  </si>
-  <si>
-    <t>AMD</t>
-  </si>
-  <si>
-    <t>QRVO</t>
-  </si>
-  <si>
-    <t>HUM</t>
-  </si>
-  <si>
-    <t>NFLX</t>
-  </si>
-  <si>
-    <t>ADBE</t>
-  </si>
-  <si>
-    <t>DPZ</t>
-  </si>
-  <si>
-    <t>WST</t>
-  </si>
-  <si>
-    <t>2020-12-01</t>
-  </si>
-  <si>
-    <t>2020-12-17</t>
-  </si>
-  <si>
-    <t>2020-10-30</t>
-  </si>
-  <si>
-    <t>2020-12-02</t>
-  </si>
-  <si>
-    <t>2020-10-27</t>
-  </si>
-  <si>
-    <t>2020-11-04</t>
-  </si>
-  <si>
-    <t>2020-11-03</t>
-  </si>
-  <si>
-    <t>2020-10-20</t>
-  </si>
-  <si>
-    <t>2020-12-10</t>
-  </si>
-  <si>
-    <t>2020-10-08</t>
-  </si>
-  <si>
-    <t>2020-10-22</t>
+    <t>ACGL</t>
+  </si>
+  <si>
+    <t>CMG</t>
+  </si>
+  <si>
+    <t>CPRT</t>
+  </si>
+  <si>
+    <t>TER</t>
+  </si>
+  <si>
+    <t>CDNS</t>
+  </si>
+  <si>
+    <t>EPAM</t>
+  </si>
+  <si>
+    <t>LHX</t>
+  </si>
+  <si>
+    <t>EL</t>
+  </si>
+  <si>
+    <t>EQIX</t>
+  </si>
+  <si>
+    <t>ENPH</t>
+  </si>
+  <si>
+    <t>DAY</t>
+  </si>
+  <si>
+    <t>APO</t>
+  </si>
+  <si>
+    <t>BLDR</t>
+  </si>
+  <si>
+    <t>FICO</t>
+  </si>
+  <si>
+    <t>MV</t>
+  </si>
+  <si>
+    <t>2020-02-11</t>
+  </si>
+  <si>
+    <t>2020-02-04</t>
+  </si>
+  <si>
+    <t>2020-02-19</t>
+  </si>
+  <si>
+    <t>2020-01-22</t>
+  </si>
+  <si>
+    <t>2020-02-12</t>
+  </si>
+  <si>
+    <t>2020-02-20</t>
+  </si>
+  <si>
+    <t>2020-02-06</t>
+  </si>
+  <si>
+    <t>2020-02-18</t>
+  </si>
+  <si>
+    <t>2020-02-05</t>
+  </si>
+  <si>
+    <t>2020-01-30</t>
+  </si>
+  <si>
+    <t>Financial Services</t>
+  </si>
+  <si>
+    <t>Consumer Cyclical</t>
+  </si>
+  <si>
+    <t>Industrials</t>
   </si>
   <si>
     <t>Technology</t>
   </si>
   <si>
-    <t>Industrials</t>
-  </si>
-  <si>
-    <t>Communication Services</t>
-  </si>
-  <si>
-    <t>Healthcare</t>
-  </si>
-  <si>
-    <t>Consumer Cyclical</t>
+    <t>Consumer Defensive</t>
+  </si>
+  <si>
+    <t>Real Estate</t>
+  </si>
+  <si>
+    <t>Insurance - Diversified</t>
+  </si>
+  <si>
+    <t>Restaurants</t>
+  </si>
+  <si>
+    <t>Specialty Business Services</t>
+  </si>
+  <si>
+    <t>Semiconductor Equipment &amp; Materials</t>
   </si>
   <si>
     <t>Software - Application</t>
   </si>
   <si>
-    <t>Integrated Freight &amp; Logistics</t>
-  </si>
-  <si>
-    <t>Telecom Services</t>
-  </si>
-  <si>
-    <t>Software - Infrastructure</t>
-  </si>
-  <si>
-    <t>Semiconductors</t>
-  </si>
-  <si>
-    <t>Healthcare Plans</t>
-  </si>
-  <si>
-    <t>Entertainment</t>
-  </si>
-  <si>
-    <t>Restaurants</t>
-  </si>
-  <si>
-    <t>Medical Instruments &amp; Supplies</t>
+    <t>Information Technology Services</t>
+  </si>
+  <si>
+    <t>Aerospace &amp; Defense</t>
+  </si>
+  <si>
+    <t>Household &amp; Personal Products</t>
+  </si>
+  <si>
+    <t>REIT - Specialty</t>
+  </si>
+  <si>
+    <t>Solar</t>
+  </si>
+  <si>
+    <t>Asset Management</t>
+  </si>
+  <si>
+    <t>Building Products &amp; Equipment</t>
   </si>
 </sst>
 </file>
@@ -590,7 +611,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AK12"/>
+  <dimension ref="A1:AK15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:37">
@@ -711,43 +732,43 @@
         <v>37</v>
       </c>
       <c r="B2">
-        <v>94.32048681541582</v>
+        <v>91.26016260162602</v>
       </c>
       <c r="C2">
-        <v>109</v>
+        <v>341</v>
       </c>
       <c r="D2">
-        <v>251.32</v>
+        <v>43.6</v>
       </c>
       <c r="E2">
-        <v>2.56</v>
+        <v>0.88</v>
       </c>
       <c r="F2">
-        <v>0.04644274468383571</v>
+        <v>-0.5295499239924993</v>
       </c>
       <c r="G2">
-        <v>4.05</v>
+        <v>1.09</v>
       </c>
       <c r="H2">
-        <v>1.325771824562705</v>
+        <v>-0.6733355517215762</v>
       </c>
       <c r="I2">
-        <v>245.1460021972656</v>
+        <v>43.27199935913086</v>
       </c>
       <c r="J2">
-        <v>248.4890014648437</v>
+        <v>42.53749980926514</v>
       </c>
       <c r="K2">
-        <v>226.1248013305664</v>
+        <v>41.71280014038086</v>
       </c>
       <c r="L2">
-        <v>185.2484003448486</v>
+        <v>38.41699998855591</v>
       </c>
       <c r="M2">
-        <v>0.99</v>
+        <v>1.02</v>
       </c>
       <c r="N2">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -759,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T2">
-        <v>1.666666666666667</v>
+        <v>0</v>
       </c>
       <c r="U2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V2" t="b">
         <v>1</v>
@@ -774,46 +795,46 @@
         <v>0</v>
       </c>
       <c r="X2">
-        <v>115.29</v>
+        <v>26.29</v>
       </c>
       <c r="Y2">
-        <v>284.5</v>
+        <v>43.63</v>
       </c>
       <c r="Z2">
-        <v>179.65</v>
+        <v>17.35</v>
       </c>
       <c r="AA2">
-        <v>-1401.66</v>
+        <v>11.47</v>
       </c>
       <c r="AB2">
-        <v>125.89</v>
+        <v>53.98</v>
       </c>
       <c r="AC2">
-        <v>2516.67</v>
+        <v>216.67</v>
       </c>
       <c r="AD2">
-        <v>6.83</v>
+        <v>3.55</v>
       </c>
       <c r="AE2">
-        <v>2536.36</v>
+        <v>-16.67</v>
       </c>
       <c r="AF2">
-        <v>130.56</v>
+        <v>4.59</v>
       </c>
       <c r="AG2">
-        <v>-200</v>
+        <v>263.33</v>
       </c>
       <c r="AH2" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="AI2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="AJ2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="AK2">
-        <v>91.11111111111111</v>
+        <v>49.3793357787714</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -821,109 +842,109 @@
         <v>38</v>
       </c>
       <c r="B3">
-        <v>95.53752535496957</v>
+        <v>94.10569105691057</v>
       </c>
       <c r="C3">
-        <v>192</v>
+        <v>20</v>
       </c>
       <c r="D3">
-        <v>251.52</v>
+        <v>17.25</v>
       </c>
       <c r="E3">
-        <v>2.22</v>
+        <v>0.88</v>
       </c>
       <c r="F3">
-        <v>-0.4799083617329645</v>
+        <v>-0.5295499239924993</v>
       </c>
       <c r="G3">
-        <v>2.2</v>
+        <v>1.36</v>
       </c>
       <c r="H3">
-        <v>-0.4070128016319675</v>
+        <v>-0.4040013310329457</v>
       </c>
       <c r="I3">
-        <v>250.7700012207031</v>
+        <v>17.21052017211914</v>
       </c>
       <c r="J3">
-        <v>238.3315002441406</v>
+        <v>16.76599998474121</v>
       </c>
       <c r="K3">
-        <v>211.2584005737305</v>
+        <v>16.05356397628784</v>
       </c>
       <c r="L3">
-        <v>155.6589000701904</v>
+        <v>15.40570795059204</v>
       </c>
       <c r="M3">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="N3">
-        <v>1.19</v>
+        <v>1.07</v>
       </c>
       <c r="P3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q3">
         <v>0</v>
       </c>
       <c r="R3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="T3">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="U3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V3" t="b">
         <v>1</v>
       </c>
       <c r="W3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X3">
-        <v>88.69</v>
+        <v>9.91</v>
       </c>
       <c r="Y3">
-        <v>259.95</v>
+        <v>17.54</v>
       </c>
       <c r="Z3">
-        <v>57.82</v>
+        <v>23.86</v>
       </c>
       <c r="AA3">
-        <v>3.4</v>
+        <v>39.02</v>
       </c>
       <c r="AB3">
-        <v>73.72</v>
+        <v>41.04</v>
       </c>
       <c r="AC3">
-        <v>120.93</v>
+        <v>206.03</v>
       </c>
       <c r="AD3">
-        <v>6.4</v>
+        <v>6.08</v>
       </c>
       <c r="AE3">
-        <v>465.38</v>
+        <v>8.23</v>
       </c>
       <c r="AF3">
-        <v>-207.44</v>
+        <v>3.14</v>
       </c>
       <c r="AG3">
-        <v>-43.72</v>
+        <v>174.14</v>
       </c>
       <c r="AH3" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="AI3" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="AJ3" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="AK3">
-        <v>75.16589343980975</v>
+        <v>45.10124625621713</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -931,49 +952,49 @@
         <v>39</v>
       </c>
       <c r="B4">
-        <v>90.66937119675457</v>
+        <v>97.76422764227642</v>
       </c>
       <c r="C4">
-        <v>361</v>
+        <v>95</v>
       </c>
       <c r="D4">
-        <v>624.34</v>
+        <v>23.82</v>
       </c>
       <c r="E4">
-        <v>1.69</v>
+        <v>0.95</v>
       </c>
       <c r="F4">
-        <v>-1.300396851147389</v>
+        <v>-0.4240704675874894</v>
       </c>
       <c r="G4">
-        <v>1.21</v>
+        <v>1.09</v>
       </c>
       <c r="H4">
-        <v>-1.334286736730739</v>
+        <v>-0.6733355517215762</v>
       </c>
       <c r="I4">
-        <v>620.95</v>
+        <v>23.44100036621094</v>
       </c>
       <c r="J4">
-        <v>616.3150024414062</v>
+        <v>22.78375034332275</v>
       </c>
       <c r="K4">
-        <v>603.8185974121094</v>
+        <v>21.98505016326904</v>
       </c>
       <c r="L4">
-        <v>526.5034994506836</v>
+        <v>19.37418758869171</v>
       </c>
       <c r="M4">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N4">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="P4">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R4">
         <v>0</v>
@@ -982,7 +1003,7 @@
         <v>0</v>
       </c>
       <c r="T4">
-        <v>3.888888888888888</v>
+        <v>0</v>
       </c>
       <c r="U4" t="b">
         <v>1</v>
@@ -991,49 +1012,49 @@
         <v>1</v>
       </c>
       <c r="W4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X4">
-        <v>345.67</v>
+        <v>12.22</v>
       </c>
       <c r="Y4">
-        <v>635.86</v>
+        <v>23.97</v>
       </c>
       <c r="Z4">
-        <v>107.57</v>
+        <v>19.72</v>
       </c>
       <c r="AA4">
-        <v>-34.05</v>
+        <v>262.15</v>
       </c>
       <c r="AB4">
-        <v>38.47</v>
+        <v>19.84</v>
       </c>
       <c r="AC4">
-        <v>110.17</v>
+        <v>64.91</v>
       </c>
       <c r="AD4">
-        <v>2.41</v>
+        <v>11.32</v>
       </c>
       <c r="AE4">
-        <v>94.76000000000001</v>
+        <v>42.42</v>
       </c>
       <c r="AF4">
-        <v>-41.95</v>
+        <v>-22.35</v>
       </c>
       <c r="AG4">
-        <v>85.88</v>
+        <v>49.12</v>
       </c>
       <c r="AH4" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="AI4" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="AJ4" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="AK4">
-        <v>59.58285446438174</v>
+        <v>28.89337692820154</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1041,109 +1062,109 @@
         <v>40</v>
       </c>
       <c r="B5">
-        <v>98.37728194726166</v>
+        <v>99.1869918699187</v>
       </c>
       <c r="C5">
-        <v>156</v>
+        <v>278</v>
       </c>
       <c r="D5">
-        <v>137.32</v>
+        <v>68.26000000000001</v>
       </c>
       <c r="E5">
-        <v>3.09</v>
+        <v>1.33</v>
       </c>
       <c r="F5">
-        <v>0.8669312340982596</v>
+        <v>0.1485322957539941</v>
       </c>
       <c r="G5">
-        <v>3.75</v>
+        <v>1.55</v>
       </c>
       <c r="H5">
-        <v>1.044779723017623</v>
+        <v>-0.2144698424002057</v>
       </c>
       <c r="I5">
-        <v>136.2779998779297</v>
+        <v>67.95200195312501</v>
       </c>
       <c r="J5">
-        <v>132.8929996490479</v>
+        <v>68.25150032043457</v>
       </c>
       <c r="K5">
-        <v>119.1124998474121</v>
+        <v>65.3718000793457</v>
       </c>
       <c r="L5">
-        <v>82.7649748802185</v>
+        <v>54.20030004501343</v>
       </c>
       <c r="M5">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="N5">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="P5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q5">
         <v>0</v>
       </c>
       <c r="R5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T5">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="U5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V5" t="b">
         <v>1</v>
       </c>
       <c r="W5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X5">
-        <v>31.95</v>
+        <v>30.84</v>
       </c>
       <c r="Y5">
-        <v>153.1</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="Z5">
-        <v>24.53</v>
+        <v>10.45</v>
       </c>
       <c r="AA5">
-        <v>0.15</v>
+        <v>205.62</v>
       </c>
       <c r="AB5">
-        <v>91.18000000000001</v>
+        <v>47.87</v>
       </c>
       <c r="AC5">
-        <v>17.65</v>
+        <v>2.56</v>
       </c>
       <c r="AD5">
-        <v>-3.77</v>
+        <v>9.16</v>
       </c>
       <c r="AE5">
-        <v>-55.56</v>
+        <v>40.35</v>
       </c>
       <c r="AF5">
-        <v>-156.25</v>
+        <v>-9.52</v>
       </c>
       <c r="AG5">
-        <v>194.12</v>
+        <v>-19.23</v>
       </c>
       <c r="AH5" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="AI5" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="AJ5" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="AK5">
-        <v>59.51877177509589</v>
+        <v>27.23564550356697</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1151,46 +1172,46 @@
         <v>41</v>
       </c>
       <c r="B6">
-        <v>99.18864097363083</v>
+        <v>92.07317073170732</v>
       </c>
       <c r="C6">
-        <v>5</v>
+        <v>287</v>
       </c>
       <c r="D6">
-        <v>81.98999999999999</v>
+        <v>73.36</v>
       </c>
       <c r="E6">
-        <v>3.25</v>
+        <v>1.07</v>
       </c>
       <c r="F6">
-        <v>1.114625872412048</v>
+        <v>-0.2432485423217577</v>
       </c>
       <c r="G6">
-        <v>4.27</v>
+        <v>1.55</v>
       </c>
       <c r="H6">
-        <v>1.531832699029099</v>
+        <v>-0.2144698424002057</v>
       </c>
       <c r="I6">
-        <v>79.4239990234375</v>
+        <v>71.59599914550782</v>
       </c>
       <c r="J6">
-        <v>79.15750083923339</v>
+        <v>69.87449951171875</v>
       </c>
       <c r="K6">
-        <v>79.72419998168945</v>
+        <v>68.26899993896484</v>
       </c>
       <c r="L6">
-        <v>57.8475</v>
+        <v>68.10859981536865</v>
       </c>
       <c r="M6">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="N6">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q6">
         <v>0</v>
@@ -1202,7 +1223,7 @@
         <v>0</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>0.5555555555555555</v>
       </c>
       <c r="U6" t="b">
         <v>0</v>
@@ -1211,49 +1232,49 @@
         <v>1</v>
       </c>
       <c r="W6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X6">
-        <v>27.43</v>
+        <v>43.29</v>
       </c>
       <c r="Y6">
-        <v>94.28</v>
+        <v>77.08</v>
       </c>
       <c r="Z6">
-        <v>64.55</v>
+        <v>18.55</v>
       </c>
       <c r="AA6">
-        <v>-8.029999999999999</v>
+        <v>65.53</v>
       </c>
       <c r="AB6">
-        <v>86.20999999999999</v>
+        <v>28.93</v>
       </c>
       <c r="AC6">
-        <v>18.18</v>
+        <v>2.78</v>
       </c>
       <c r="AD6">
-        <v>4.75</v>
+        <v>6.86</v>
       </c>
       <c r="AE6">
-        <v>-7.14</v>
+        <v>-5.13</v>
       </c>
       <c r="AF6">
-        <v>-12.5</v>
+        <v>-11.36</v>
       </c>
       <c r="AG6">
-        <v>45.45</v>
+        <v>22.22</v>
       </c>
       <c r="AH6" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="AI6" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="AJ6" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="AK6">
-        <v>55.69591236965997</v>
+        <v>20.47272062946137</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1261,43 +1282,43 @@
         <v>42</v>
       </c>
       <c r="B7">
-        <v>95.13184584178499</v>
+        <v>94.91869918699187</v>
       </c>
       <c r="C7">
-        <v>337</v>
+        <v>477</v>
       </c>
       <c r="D7">
-        <v>129.01</v>
+        <v>223.29</v>
       </c>
       <c r="E7">
-        <v>3.68</v>
+        <v>1.2</v>
       </c>
       <c r="F7">
-        <v>1.780305212880355</v>
+        <v>-0.04735812328388198</v>
       </c>
       <c r="G7">
-        <v>2.97</v>
+        <v>1.95</v>
       </c>
       <c r="H7">
-        <v>0.31420025900041</v>
+        <v>0.1845438178792469</v>
       </c>
       <c r="I7">
-        <v>127.7659973144531</v>
+        <v>218.3759979248047</v>
       </c>
       <c r="J7">
-        <v>125.9790000915527</v>
+        <v>213.1239997863769</v>
       </c>
       <c r="K7">
-        <v>127.1438995361328</v>
+        <v>204.5705996704102</v>
       </c>
       <c r="L7">
-        <v>108.3098247528076</v>
+        <v>186.513099899292</v>
       </c>
       <c r="M7">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N7">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="P7">
         <v>0</v>
@@ -1315,55 +1336,55 @@
         <v>0</v>
       </c>
       <c r="U7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V7" t="b">
         <v>1</v>
       </c>
       <c r="W7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X7">
-        <v>67.54000000000001</v>
+        <v>126.37</v>
       </c>
       <c r="Y7">
-        <v>136.06</v>
+        <v>224.22</v>
       </c>
       <c r="Z7">
-        <v>12.9</v>
+        <v>10.55</v>
       </c>
       <c r="AA7">
-        <v>24.24</v>
+        <v>25.58</v>
       </c>
       <c r="AB7">
-        <v>43.83</v>
+        <v>16.2</v>
       </c>
       <c r="AC7">
-        <v>19.72</v>
+        <v>9.91</v>
       </c>
       <c r="AD7">
-        <v>2.23</v>
+        <v>4.49</v>
       </c>
       <c r="AE7">
-        <v>97.67</v>
+        <v>14.02</v>
       </c>
       <c r="AF7">
-        <v>-69.06</v>
+        <v>-4.46</v>
       </c>
       <c r="AG7">
-        <v>95.77</v>
+        <v>0.9</v>
       </c>
       <c r="AH7" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="AI7" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="AJ7" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="AK7">
-        <v>48.23300526478153</v>
+        <v>17.10129477674057</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1371,43 +1392,43 @@
         <v>43</v>
       </c>
       <c r="B8">
-        <v>92.2920892494929</v>
+        <v>90.2439024390244</v>
       </c>
       <c r="C8">
-        <v>425</v>
+        <v>271</v>
       </c>
       <c r="D8">
-        <v>413.89</v>
+        <v>212.29</v>
       </c>
       <c r="E8">
-        <v>2.01</v>
+        <v>1.27</v>
       </c>
       <c r="F8">
-        <v>-0.8050075745198124</v>
+        <v>0.05812133312112819</v>
       </c>
       <c r="G8">
-        <v>1.62</v>
+        <v>1.37</v>
       </c>
       <c r="H8">
-        <v>-0.9502641979524598</v>
+        <v>-0.3940259895259593</v>
       </c>
       <c r="I8">
-        <v>400.6480041503906</v>
+        <v>211.6999969482422</v>
       </c>
       <c r="J8">
-        <v>401.6655014038086</v>
+        <v>202.8254989624023</v>
       </c>
       <c r="K8">
-        <v>405.0408013916016</v>
+        <v>200.2051998901367</v>
       </c>
       <c r="L8">
-        <v>371.3386996459961</v>
+        <v>195.2341500854492</v>
       </c>
       <c r="M8">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="N8">
-        <v>0.99</v>
+        <v>1.06</v>
       </c>
       <c r="P8">
         <v>0</v>
@@ -1431,49 +1452,49 @@
         <v>1</v>
       </c>
       <c r="W8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X8">
-        <v>208.25</v>
+        <v>133.13</v>
       </c>
       <c r="Y8">
-        <v>431.12</v>
+        <v>217.31</v>
       </c>
       <c r="Z8">
-        <v>51.58</v>
+        <v>47.03</v>
       </c>
       <c r="AA8">
-        <v>4.62</v>
+        <v>6.23</v>
       </c>
       <c r="AB8">
-        <v>12.26</v>
+        <v>26.12</v>
       </c>
       <c r="AC8">
-        <v>168.02</v>
+        <v>1.05</v>
       </c>
       <c r="AD8">
-        <v>12.68</v>
+        <v>1.9</v>
       </c>
       <c r="AE8">
-        <v>286.31</v>
+        <v>-14.6</v>
       </c>
       <c r="AF8">
-        <v>-8.210000000000001</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="AG8">
-        <v>-24.42</v>
+        <v>7.85</v>
       </c>
       <c r="AH8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="AI8" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="AJ8" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="AK8">
-        <v>46.54535299088607</v>
+        <v>15.65821441649348</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1481,43 +1502,43 @@
         <v>44</v>
       </c>
       <c r="B9">
-        <v>96.95740365111561</v>
+        <v>91.66666666666666</v>
       </c>
       <c r="C9">
-        <v>135</v>
+        <v>294</v>
       </c>
       <c r="D9">
-        <v>500.03</v>
+        <v>211.96</v>
       </c>
       <c r="E9">
-        <v>2.48</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="F9">
-        <v>-0.07740457447305861</v>
+        <v>-0.6350293803975094</v>
       </c>
       <c r="G9">
-        <v>2.96</v>
+        <v>1.14</v>
       </c>
       <c r="H9">
-        <v>0.3048338556155738</v>
+        <v>-0.6234588441866448</v>
       </c>
       <c r="I9">
-        <v>488.0239990234375</v>
+        <v>207.5580017089844</v>
       </c>
       <c r="J9">
-        <v>492.5035003662109</v>
+        <v>205.3769989013672</v>
       </c>
       <c r="K9">
-        <v>495.1472003173828</v>
+        <v>197.3395999145508</v>
       </c>
       <c r="L9">
-        <v>420.9264001464844</v>
+        <v>185.846600112915</v>
       </c>
       <c r="M9">
-        <v>0.99</v>
+        <v>1.01</v>
       </c>
       <c r="N9">
-        <v>0.99</v>
+        <v>1.05</v>
       </c>
       <c r="P9">
         <v>0</v>
@@ -1535,55 +1556,55 @@
         <v>0</v>
       </c>
       <c r="U9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V9" t="b">
         <v>1</v>
       </c>
       <c r="W9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X9">
-        <v>257.01</v>
+        <v>121.47</v>
       </c>
       <c r="Y9">
-        <v>575.37</v>
+        <v>212.02</v>
       </c>
       <c r="Z9">
-        <v>206.56</v>
+        <v>73.33</v>
       </c>
       <c r="AA9">
-        <v>445.46</v>
+        <v>6.22</v>
       </c>
       <c r="AB9">
-        <v>46.39</v>
+        <v>8.56</v>
       </c>
       <c r="AC9">
-        <v>7.24</v>
+        <v>4.43</v>
       </c>
       <c r="AD9">
-        <v>7.72</v>
+        <v>13.12</v>
       </c>
       <c r="AE9">
-        <v>1.24</v>
+        <v>275</v>
       </c>
       <c r="AF9">
-        <v>21.05</v>
+        <v>-71.23999999999999</v>
       </c>
       <c r="AG9">
-        <v>-12.5</v>
+        <v>-3.16</v>
       </c>
       <c r="AH9" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="AI9" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="AJ9" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AK9">
-        <v>43.25508230034485</v>
+        <v>4.825139835958262</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1591,43 +1612,43 @@
         <v>45</v>
       </c>
       <c r="B10">
-        <v>96.14604462474645</v>
+        <v>91.46341463414635</v>
       </c>
       <c r="C10">
-        <v>202</v>
+        <v>476</v>
       </c>
       <c r="D10">
-        <v>490.43</v>
+        <v>588.99</v>
       </c>
       <c r="E10">
-        <v>2.82</v>
+        <v>1.01</v>
       </c>
       <c r="F10">
-        <v>0.4489465319437416</v>
+        <v>-0.3336595049546235</v>
       </c>
       <c r="G10">
-        <v>2.62</v>
+        <v>1.19</v>
       </c>
       <c r="H10">
-        <v>-0.01362385946885256</v>
+        <v>-0.5735821366517132</v>
       </c>
       <c r="I10">
-        <v>483.1440002441406</v>
+        <v>584.8539916992188</v>
       </c>
       <c r="J10">
-        <v>483.6350006103515</v>
+        <v>573.6315002441406</v>
       </c>
       <c r="K10">
-        <v>470.6872009277344</v>
+        <v>561.0143981933594</v>
       </c>
       <c r="L10">
-        <v>389.6335507202148</v>
+        <v>527.1624995422363</v>
       </c>
       <c r="M10">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="N10">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="P10">
         <v>0</v>
@@ -1651,49 +1672,49 @@
         <v>1</v>
       </c>
       <c r="W10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X10">
-        <v>255.13</v>
+        <v>355.04</v>
       </c>
       <c r="Y10">
-        <v>536.88</v>
+        <v>609.97</v>
       </c>
       <c r="Z10">
-        <v>248.99</v>
+        <v>49.36</v>
       </c>
       <c r="AA10">
-        <v>77.26000000000001</v>
+        <v>-7.24</v>
       </c>
       <c r="AB10">
-        <v>7.37</v>
+        <v>9.59</v>
       </c>
       <c r="AC10">
-        <v>13.07</v>
+        <v>2.9</v>
       </c>
       <c r="AD10">
-        <v>8.15</v>
+        <v>1.38</v>
       </c>
       <c r="AE10">
-        <v>-12.72</v>
+        <v>-16.47</v>
       </c>
       <c r="AF10">
-        <v>15.15</v>
+        <v>18.06</v>
       </c>
       <c r="AG10">
-        <v>12.5</v>
+        <v>4.35</v>
       </c>
       <c r="AH10" t="s">
         <v>56</v>
       </c>
       <c r="AI10" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="AJ10" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="AK10">
-        <v>25.85292661528925</v>
+        <v>4.722336312432398</v>
       </c>
     </row>
     <row r="11" spans="1:37">
@@ -1701,43 +1722,43 @@
         <v>46</v>
       </c>
       <c r="B11">
-        <v>94.9290060851927</v>
+        <v>100</v>
       </c>
       <c r="C11">
-        <v>460</v>
+        <v>103</v>
       </c>
       <c r="D11">
-        <v>425.28</v>
+        <v>31.59</v>
       </c>
       <c r="E11">
-        <v>1.61</v>
+        <v>3.44</v>
       </c>
       <c r="F11">
-        <v>-1.424244170304283</v>
+        <v>3.32798448167644</v>
       </c>
       <c r="G11">
-        <v>1.41</v>
+        <v>5</v>
       </c>
       <c r="H11">
-        <v>-1.146958669034017</v>
+        <v>3.227022977510074</v>
       </c>
       <c r="I11">
-        <v>420.3319946289063</v>
+        <v>30.3060001373291</v>
       </c>
       <c r="J11">
-        <v>400.7774993896484</v>
+        <v>27.10300006866455</v>
       </c>
       <c r="K11">
-        <v>400.0889990234375</v>
+        <v>23.15700023651123</v>
       </c>
       <c r="L11">
-        <v>355.1028503417969</v>
+        <v>20.85880005836487</v>
       </c>
       <c r="M11">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="N11">
-        <v>1.05</v>
+        <v>1.31</v>
       </c>
       <c r="P11">
         <v>0</v>
@@ -1761,49 +1782,49 @@
         <v>1</v>
       </c>
       <c r="W11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X11">
-        <v>227.5</v>
+        <v>5.44</v>
       </c>
       <c r="Y11">
-        <v>428.54</v>
+        <v>35.42</v>
       </c>
       <c r="Z11">
-        <v>14.68</v>
+        <v>2.97</v>
       </c>
       <c r="AA11">
-        <v>15.11</v>
+        <v>-112.43</v>
       </c>
       <c r="AB11">
-        <v>1.06</v>
+        <v>371.43</v>
       </c>
       <c r="AC11">
-        <v>44.08</v>
+        <v>2400</v>
       </c>
       <c r="AD11">
-        <v>-3.61</v>
+        <v>20.42</v>
       </c>
       <c r="AE11">
-        <v>-3.18</v>
+        <v>177.78</v>
       </c>
       <c r="AF11">
-        <v>-1.88</v>
+        <v>200</v>
       </c>
       <c r="AG11">
-        <v>51.66</v>
+        <v>200</v>
       </c>
       <c r="AH11" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="AI11" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="AJ11" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="AK11">
-        <v>16.25706388182987</v>
+        <v>89.99999999999999</v>
       </c>
     </row>
     <row r="12" spans="1:37">
@@ -1811,58 +1832,61 @@
         <v>47</v>
       </c>
       <c r="B12">
-        <v>97.76876267748479</v>
+        <v>98.17073170731707</v>
       </c>
       <c r="C12">
-        <v>461</v>
+        <v>349</v>
       </c>
       <c r="D12">
-        <v>274.9</v>
+        <v>71.48</v>
       </c>
       <c r="E12">
-        <v>2.42</v>
+        <v>0.97</v>
       </c>
       <c r="F12">
-        <v>-0.1702900638407293</v>
+        <v>-0.3939334800432008</v>
       </c>
       <c r="G12">
-        <v>1.92</v>
+        <v>2.4</v>
       </c>
       <c r="H12">
-        <v>-0.6692720964073778</v>
+        <v>0.6334341856936311</v>
       </c>
       <c r="I12">
-        <v>270.8180053710938</v>
+        <v>70.17800140380859</v>
       </c>
       <c r="J12">
-        <v>273.7225006103516</v>
+        <v>66.66600036621094</v>
       </c>
       <c r="K12">
-        <v>272.4252001953125</v>
+        <v>60.29319999694824</v>
       </c>
       <c r="L12">
-        <v>202.5414496612549</v>
+        <v>53.1964999961853</v>
       </c>
       <c r="M12">
-        <v>0.99</v>
+        <v>1.05</v>
       </c>
       <c r="N12">
-        <v>0.99</v>
+        <v>1.16</v>
+      </c>
+      <c r="O12" t="s">
+        <v>51</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>18.33333333333333</v>
       </c>
       <c r="U12" t="b">
         <v>0</v>
@@ -1871,49 +1895,379 @@
         <v>1</v>
       </c>
       <c r="W12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X12">
-        <v>124.53</v>
+        <v>34.67</v>
       </c>
       <c r="Y12">
-        <v>288.65</v>
+        <v>71.67</v>
       </c>
       <c r="Z12">
-        <v>17.15</v>
+        <v>7.36</v>
       </c>
       <c r="AA12">
-        <v>25.27</v>
+        <v>-13.71</v>
       </c>
       <c r="AB12">
-        <v>0.26</v>
+        <v>190</v>
       </c>
       <c r="AC12">
-        <v>63.16</v>
+        <v>2100</v>
       </c>
       <c r="AD12">
-        <v>5.68</v>
+        <v>3.38</v>
       </c>
       <c r="AE12">
-        <v>22.77</v>
+        <v>1000</v>
       </c>
       <c r="AF12">
-        <v>17.44</v>
+        <v>-50</v>
       </c>
       <c r="AG12">
-        <v>13.16</v>
+        <v>300</v>
       </c>
       <c r="AH12" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="AI12" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="AJ12" t="s">
         <v>72</v>
       </c>
       <c r="AK12">
-        <v>12.55368260201255</v>
+        <v>89.31071901832203</v>
+      </c>
+    </row>
+    <row r="13" spans="1:37">
+      <c r="A13" t="s">
+        <v>48</v>
+      </c>
+      <c r="B13">
+        <v>96.95121951219512</v>
+      </c>
+      <c r="C13">
+        <v>297</v>
+      </c>
+      <c r="D13">
+        <v>49.81</v>
+      </c>
+      <c r="E13">
+        <v>1.46</v>
+      </c>
+      <c r="F13">
+        <v>0.3444227147918698</v>
+      </c>
+      <c r="G13">
+        <v>1.44</v>
+      </c>
+      <c r="H13">
+        <v>-0.3241985989770553</v>
+      </c>
+      <c r="I13">
+        <v>48.19600143432617</v>
+      </c>
+      <c r="J13">
+        <v>47.22500057220459</v>
+      </c>
+      <c r="K13">
+        <v>44.76000038146972</v>
+      </c>
+      <c r="L13">
+        <v>37.17560012817383</v>
+      </c>
+      <c r="M13">
+        <v>1.02</v>
+      </c>
+      <c r="N13">
+        <v>1.08</v>
+      </c>
+      <c r="P13">
+        <v>0</v>
+      </c>
+      <c r="Q13">
+        <v>0</v>
+      </c>
+      <c r="R13">
+        <v>0</v>
+      </c>
+      <c r="S13">
+        <v>0</v>
+      </c>
+      <c r="T13">
+        <v>0</v>
+      </c>
+      <c r="U13" t="b">
+        <v>0</v>
+      </c>
+      <c r="V13" t="b">
+        <v>1</v>
+      </c>
+      <c r="W13" t="b">
+        <v>0</v>
+      </c>
+      <c r="X13">
+        <v>25.75</v>
+      </c>
+      <c r="Y13">
+        <v>50.01</v>
+      </c>
+      <c r="Z13">
+        <v>7.85</v>
+      </c>
+      <c r="AA13">
+        <v>15.66</v>
+      </c>
+      <c r="AB13">
+        <v>230.16</v>
+      </c>
+      <c r="AC13">
+        <v>267.35</v>
+      </c>
+      <c r="AD13">
+        <v>22.77</v>
+      </c>
+      <c r="AE13">
+        <v>118.67</v>
+      </c>
+      <c r="AF13">
+        <v>11.94</v>
+      </c>
+      <c r="AG13">
+        <v>168.37</v>
+      </c>
+      <c r="AH13" t="s">
+        <v>61</v>
+      </c>
+      <c r="AI13" t="s">
+        <v>62</v>
+      </c>
+      <c r="AJ13" t="s">
+        <v>78</v>
+      </c>
+      <c r="AK13">
+        <v>71.98299373694243</v>
+      </c>
+    </row>
+    <row r="14" spans="1:37">
+      <c r="A14" t="s">
+        <v>49</v>
+      </c>
+      <c r="B14">
+        <v>98.78048780487805</v>
+      </c>
+      <c r="C14">
+        <v>360</v>
+      </c>
+      <c r="D14">
+        <v>26.29</v>
+      </c>
+      <c r="E14">
+        <v>1.07</v>
+      </c>
+      <c r="F14">
+        <v>-0.2432485423217577</v>
+      </c>
+      <c r="G14">
+        <v>1.72</v>
+      </c>
+      <c r="H14">
+        <v>-0.04488903678143835</v>
+      </c>
+      <c r="I14">
+        <v>25.87400016784668</v>
+      </c>
+      <c r="J14">
+        <v>25.46350011825562</v>
+      </c>
+      <c r="K14">
+        <v>25.04180004119873</v>
+      </c>
+      <c r="L14">
+        <v>19.29560001373291</v>
+      </c>
+      <c r="M14">
+        <v>1.02</v>
+      </c>
+      <c r="N14">
+        <v>1.03</v>
+      </c>
+      <c r="P14">
+        <v>0</v>
+      </c>
+      <c r="Q14">
+        <v>0</v>
+      </c>
+      <c r="R14">
+        <v>0</v>
+      </c>
+      <c r="S14">
+        <v>0</v>
+      </c>
+      <c r="T14">
+        <v>0</v>
+      </c>
+      <c r="U14" t="b">
+        <v>1</v>
+      </c>
+      <c r="V14" t="b">
+        <v>1</v>
+      </c>
+      <c r="W14" t="b">
+        <v>0</v>
+      </c>
+      <c r="X14">
+        <v>11.91</v>
+      </c>
+      <c r="Y14">
+        <v>26.62</v>
+      </c>
+      <c r="Z14">
+        <v>2.41</v>
+      </c>
+      <c r="AA14">
+        <v>704.86</v>
+      </c>
+      <c r="AB14">
+        <v>43.97</v>
+      </c>
+      <c r="AC14">
+        <v>47.83</v>
+      </c>
+      <c r="AD14">
+        <v>10.03</v>
+      </c>
+      <c r="AE14">
+        <v>17.24</v>
+      </c>
+      <c r="AF14">
+        <v>87.09999999999999</v>
+      </c>
+      <c r="AG14">
+        <v>-32.61</v>
+      </c>
+      <c r="AH14" t="s">
+        <v>57</v>
+      </c>
+      <c r="AI14" t="s">
+        <v>64</v>
+      </c>
+      <c r="AJ14" t="s">
+        <v>79</v>
+      </c>
+      <c r="AK14">
+        <v>38.95768426822708</v>
+      </c>
+    </row>
+    <row r="15" spans="1:37">
+      <c r="A15" t="s">
+        <v>50</v>
+      </c>
+      <c r="B15">
+        <v>98.3739837398374</v>
+      </c>
+      <c r="C15">
+        <v>485</v>
+      </c>
+      <c r="D15">
+        <v>401.51</v>
+      </c>
+      <c r="E15">
+        <v>0.9</v>
+      </c>
+      <c r="F15">
+        <v>-0.4994129364482108</v>
+      </c>
+      <c r="G15">
+        <v>1.86</v>
+      </c>
+      <c r="H15">
+        <v>0.09476574431637021</v>
+      </c>
+      <c r="I15">
+        <v>389.45</v>
+      </c>
+      <c r="J15">
+        <v>374.3650009155273</v>
+      </c>
+      <c r="K15">
+        <v>355.8405999755859</v>
+      </c>
+      <c r="L15">
+        <v>323.0805500793457</v>
+      </c>
+      <c r="M15">
+        <v>1.04</v>
+      </c>
+      <c r="N15">
+        <v>1.09</v>
+      </c>
+      <c r="P15">
+        <v>0</v>
+      </c>
+      <c r="Q15">
+        <v>0</v>
+      </c>
+      <c r="R15">
+        <v>0</v>
+      </c>
+      <c r="S15">
+        <v>0</v>
+      </c>
+      <c r="T15">
+        <v>0</v>
+      </c>
+      <c r="U15" t="b">
+        <v>0</v>
+      </c>
+      <c r="V15" t="b">
+        <v>1</v>
+      </c>
+      <c r="W15" t="b">
+        <v>0</v>
+      </c>
+      <c r="X15">
+        <v>197.34</v>
+      </c>
+      <c r="Y15">
+        <v>405</v>
+      </c>
+      <c r="Z15">
+        <v>9.19</v>
+      </c>
+      <c r="AA15">
+        <v>12.55</v>
+      </c>
+      <c r="AB15">
+        <v>17.55</v>
+      </c>
+      <c r="AC15">
+        <v>36.96</v>
+      </c>
+      <c r="AD15">
+        <v>18.84</v>
+      </c>
+      <c r="AE15">
+        <v>-14.48</v>
+      </c>
+      <c r="AF15">
+        <v>92.17</v>
+      </c>
+      <c r="AG15">
+        <v>-16.67</v>
+      </c>
+      <c r="AH15" t="s">
+        <v>61</v>
+      </c>
+      <c r="AI15" t="s">
+        <v>65</v>
+      </c>
+      <c r="AJ15" t="s">
+        <v>72</v>
+      </c>
+      <c r="AK15">
+        <v>24.41221104731349</v>
       </c>
     </row>
   </sheetData>
